--- a/EXCEL/class notes/day8 index & conditional formatting/Conditional format Date.xlsx
+++ b/EXCEL/class notes/day8 index & conditional formatting/Conditional format Date.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Kamal\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analyst\EXCEL\class notes\day8 index &amp; conditional formatting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C59604E-16B6-43E7-AB8A-AB18C273F781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747D3532-0D26-4C87-84C9-1306C3CAD2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="906" firstSheet="3" activeTab="12" xr2:uid="{DDBE9BB9-C8F2-4344-8B14-705FB3F3B897}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="906" firstSheet="2" activeTab="12" xr2:uid="{DDBE9BB9-C8F2-4344-8B14-705FB3F3B897}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1 (2)" sheetId="12" r:id="rId1"/>
@@ -31,6 +31,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -643,13 +652,34 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="310">
+  <dxfs count="114">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
@@ -657,7 +687,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -672,13 +702,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -691,21 +714,14 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -715,14 +731,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -739,14 +748,14 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -756,14 +765,41 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -778,11 +814,43 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -795,25 +863,9 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
+      <font>
+        <color theme="0"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -828,7 +880,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -843,9 +895,19 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -860,9 +922,12 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -877,9 +942,39 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -894,27 +989,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -925,13 +999,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -942,33 +1009,12 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -983,9 +1029,36 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1014,13 +1087,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -1031,20 +1097,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -1055,23 +1107,22 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1086,13 +1137,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -1103,21 +1147,24 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
-        <color theme="0"/>
+        <color rgb="FF006100"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
-        <color theme="0"/>
+        <color rgb="FF006100"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1131,8 +1178,37 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="0"/>
+        <color rgb="FF006100"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1146,8 +1222,37 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="0"/>
+        <color rgb="FF006100"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1161,18 +1266,37 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color theme="0"/>
+        <color rgb="FF9C5700"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1186,8 +1310,37 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="0"/>
+        <color rgb="FF006100"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1201,1610 +1354,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2826,88 +1375,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2915,243 +1383,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3757,13 +1988,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9E082B8-0DD1-4A7E-8692-2558994EE551}">
   <dimension ref="B1:S36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="12" max="12" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>57</v>
       </c>
@@ -3798,7 +2029,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>13</v>
       </c>
@@ -3824,7 +2055,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>24</v>
       </c>
@@ -3853,7 +2084,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>34</v>
       </c>
@@ -3882,7 +2113,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>46</v>
       </c>
@@ -3911,7 +2142,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>53</v>
       </c>
@@ -3940,7 +2171,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>99</v>
       </c>
@@ -3969,7 +2200,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>10</v>
       </c>
@@ -3998,7 +2229,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>100</v>
       </c>
@@ -4027,7 +2258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>92</v>
       </c>
@@ -4056,7 +2287,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>3</v>
       </c>
@@ -4085,7 +2316,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>36</v>
       </c>
@@ -4114,7 +2345,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>46</v>
       </c>
@@ -4143,7 +2374,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>93</v>
       </c>
@@ -4172,7 +2403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>22</v>
       </c>
@@ -4201,7 +2432,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>61</v>
       </c>
@@ -4230,7 +2461,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>66</v>
       </c>
@@ -4259,7 +2490,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>24</v>
       </c>
@@ -4288,7 +2519,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>34</v>
       </c>
@@ -4317,7 +2548,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>46</v>
       </c>
@@ -4346,7 +2577,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>53</v>
       </c>
@@ -4375,7 +2606,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>99</v>
       </c>
@@ -4404,7 +2635,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>10</v>
       </c>
@@ -4433,7 +2664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>100</v>
       </c>
@@ -4462,7 +2693,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>92</v>
       </c>
@@ -4491,7 +2722,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>3</v>
       </c>
@@ -4520,7 +2751,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>36</v>
       </c>
@@ -4549,7 +2780,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>46</v>
       </c>
@@ -4578,7 +2809,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>93</v>
       </c>
@@ -4607,7 +2838,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>22</v>
       </c>
@@ -4636,7 +2867,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>61</v>
       </c>
@@ -4665,7 +2896,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>66</v>
       </c>
@@ -4696,63 +2927,63 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:B18">
-    <cfRule type="cellIs" dxfId="309" priority="13" operator="lessThan">
+    <cfRule type="cellIs" dxfId="113" priority="13" operator="lessThan">
       <formula>35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D18">
-    <cfRule type="cellIs" dxfId="308" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="112" priority="12" operator="greaterThan">
       <formula>34</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="307" priority="11" operator="lessThan">
+    <cfRule type="cellIs" dxfId="111" priority="11" operator="lessThan">
       <formula>35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="cellIs" dxfId="306" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="110" priority="10" operator="greaterThan">
       <formula>34</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F18">
-    <cfRule type="cellIs" dxfId="305" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="109" priority="8" operator="greaterThan">
       <formula>34</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="304" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="108" priority="9" operator="lessThan">
       <formula>35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H18">
-    <cfRule type="cellIs" dxfId="303" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="107" priority="7" operator="between">
       <formula>35</formula>
       <formula>59</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K18">
-    <cfRule type="cellIs" dxfId="302" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="106" priority="6" operator="between">
       <formula>60</formula>
       <formula>74</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:M18">
-    <cfRule type="cellIs" dxfId="301" priority="5" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="105" priority="5" operator="greaterThanOrEqual">
       <formula>75</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4:O18">
-    <cfRule type="cellIs" dxfId="300" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="4" operator="equal">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4:Q18">
-    <cfRule type="containsText" dxfId="299" priority="3" operator="containsText" text="A">
+    <cfRule type="containsText" dxfId="103" priority="3" operator="containsText" text="A">
       <formula>NOT(ISERROR(SEARCH("A",Q4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S4:S18">
-    <cfRule type="uniqueValues" dxfId="298" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="297" priority="2"/>
+    <cfRule type="uniqueValues" dxfId="102" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4761,9 +2992,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ED41C8F-E1E3-49E8-BABE-2C7C5CC11C6E}">
   <dimension ref="A1:O16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>24</v>
       </c>
@@ -4783,7 +3014,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>19</v>
       </c>
@@ -4816,7 +3047,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>22</v>
       </c>
@@ -4849,7 +3080,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>11</v>
       </c>
@@ -4882,7 +3113,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>27</v>
       </c>
@@ -4915,7 +3146,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>13</v>
       </c>
@@ -4948,7 +3179,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>8</v>
       </c>
@@ -4981,7 +3212,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>27</v>
       </c>
@@ -5014,7 +3245,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>2</v>
       </c>
@@ -5047,7 +3278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>14</v>
       </c>
@@ -5080,7 +3311,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>26</v>
       </c>
@@ -5113,7 +3344,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>23</v>
       </c>
@@ -5146,7 +3377,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>27</v>
       </c>
@@ -5179,7 +3410,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>17</v>
       </c>
@@ -5206,7 +3437,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>1</v>
       </c>
@@ -5233,7 +3464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>22</v>
       </c>
@@ -5262,20 +3493,20 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A16">
-    <cfRule type="uniqueValues" dxfId="278" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="277" priority="6"/>
+    <cfRule type="uniqueValues" dxfId="32" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D16">
-    <cfRule type="cellIs" dxfId="276" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="4" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J16">
-    <cfRule type="uniqueValues" dxfId="275" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="274" priority="3"/>
+    <cfRule type="uniqueValues" dxfId="29" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O16">
-    <cfRule type="duplicateValues" dxfId="273" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5284,9 +3515,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6992248-58CB-4718-B438-5DDA4385F2FC}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>51</v>
       </c>
@@ -5312,13 +3543,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B2" s="6">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>35</v>
@@ -5339,13 +3570,13 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B3" s="6">
         <f t="shared" ref="B3:B9" ca="1" si="0">RANDBETWEEN(1,100)</f>
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>36</v>
@@ -5366,13 +3597,13 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>37</v>
@@ -5393,13 +3624,13 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>38</v>
       </c>
       <c r="B5" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>38</v>
@@ -5420,13 +3651,13 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B6" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>39</v>
@@ -5447,13 +3678,13 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B7" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>40</v>
@@ -5474,13 +3705,13 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B8" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -5501,13 +3732,13 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>42</v>
       </c>
       <c r="B9" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>42</v>
@@ -5531,22 +3762,22 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B2:B9">
-    <cfRule type="cellIs" dxfId="64" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="5" operator="lessThan">
       <formula>35</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F9">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="lessThan">
+      <formula>35</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I2:I9">
-    <cfRule type="cellIs" dxfId="63" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="3" operator="lessThan">
       <formula>35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L9">
-    <cfRule type="cellIs" dxfId="62" priority="2" operator="lessThan">
-      <formula>35</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
-    <cfRule type="cellIs" dxfId="57" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="lessThan">
       <formula>35</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5557,23 +3788,23 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A3ED325-E997-421F-A7DE-490DDC72EC37}">
   <dimension ref="C1:X18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:24" x14ac:dyDescent="0.3">
       <c r="L1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>2</v>
       </c>
@@ -5593,36 +3824,36 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
         <f ca="1">TODAY()</f>
-        <v>45645</v>
+        <v>45925</v>
       </c>
       <c r="F4" s="5">
         <f ca="1">YEAR(C4)</f>
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G4" s="5">
         <f ca="1">MONTH(C4)</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5">
         <f ca="1">DAY(C4)</f>
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J4" s="4">
         <f ca="1">DATE(F4,G4,H4)</f>
-        <v>45645</v>
-      </c>
-    </row>
-    <row r="5" spans="3:24" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="5" spans="3:24" x14ac:dyDescent="0.3">
       <c r="L5" s="1">
         <f ca="1">DATE(RANDBETWEEN(2022,2025),RANDBETWEEN(1,12),RANDBETWEEN(1,28))</f>
-        <v>45532</v>
+        <v>45500</v>
       </c>
       <c r="P5" s="7">
         <f ca="1">DATE(RANDBETWEEN(2022,2025),RANDBETWEEN(1,12),RANDBETWEEN(1,28))</f>
-        <v>44947</v>
+        <v>44966</v>
       </c>
       <c r="R5" s="7">
         <v>44562</v>
@@ -5632,37 +3863,37 @@
       </c>
       <c r="V5" s="1">
         <f ca="1">RANDBETWEEN(44562,45022)</f>
-        <v>45015</v>
-      </c>
-    </row>
-    <row r="6" spans="3:24" x14ac:dyDescent="0.35">
+        <v>44871</v>
+      </c>
+    </row>
+    <row r="6" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C6" s="2" t="s">
         <v>0</v>
       </c>
       <c r="L6" s="1">
         <f t="shared" ref="L6:L18" ca="1" si="0">DATE(RANDBETWEEN(2022,2025),RANDBETWEEN(1,12),RANDBETWEEN(1,28))</f>
-        <v>45350</v>
+        <v>44599</v>
       </c>
       <c r="P6" s="7">
         <f t="shared" ref="P6:P17" ca="1" si="1">DATE(RANDBETWEEN(2022,2025),RANDBETWEEN(1,12),RANDBETWEEN(1,28))</f>
-        <v>44729</v>
+        <v>45848</v>
       </c>
       <c r="V6" s="1">
         <f t="shared" ref="V6:V9" ca="1" si="2">RANDBETWEEN(44562,45022)</f>
-        <v>44785</v>
-      </c>
-    </row>
-    <row r="7" spans="3:24" x14ac:dyDescent="0.35">
+        <v>44577</v>
+      </c>
+    </row>
+    <row r="7" spans="3:24" x14ac:dyDescent="0.3">
       <c r="L7" s="1">
         <f ca="1">TODAY()</f>
-        <v>45645</v>
+        <v>45925</v>
       </c>
       <c r="N7" t="s">
         <v>2</v>
       </c>
       <c r="P7" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>45962</v>
+        <v>45787</v>
       </c>
       <c r="R7" s="7">
         <v>46022</v>
@@ -5672,54 +3903,54 @@
       </c>
       <c r="V7" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>44807</v>
-      </c>
-    </row>
-    <row r="8" spans="3:24" x14ac:dyDescent="0.35">
+        <v>44792</v>
+      </c>
+    </row>
+    <row r="8" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>45353</v>
       </c>
       <c r="L8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45085</v>
+        <v>45850</v>
       </c>
       <c r="P8" s="7">
         <f ca="1">P9-1</f>
-        <v>45644</v>
+        <v>45924</v>
       </c>
       <c r="V8" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>44575</v>
-      </c>
-    </row>
-    <row r="9" spans="3:24" x14ac:dyDescent="0.35">
+        <v>44600</v>
+      </c>
+    </row>
+    <row r="9" spans="3:24" x14ac:dyDescent="0.3">
       <c r="L9" s="1">
         <f ca="1">L7-1</f>
-        <v>45644</v>
+        <v>45924</v>
       </c>
       <c r="N9" t="s">
         <v>9</v>
       </c>
       <c r="P9" s="7">
         <f ca="1">TODAY()</f>
-        <v>45645</v>
+        <v>45925</v>
       </c>
       <c r="V9" s="1">
         <f t="shared" ca="1" si="2"/>
-        <v>44922</v>
-      </c>
-    </row>
-    <row r="10" spans="3:24" x14ac:dyDescent="0.35">
+        <v>45005</v>
+      </c>
+    </row>
+    <row r="10" spans="3:24" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>1</v>
       </c>
       <c r="L10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45682</v>
+        <v>45711</v>
       </c>
       <c r="P10" s="7">
         <f ca="1">P9+1</f>
-        <v>45646</v>
+        <v>45926</v>
       </c>
       <c r="T10">
         <f>T7-T5</f>
@@ -5736,123 +3967,123 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="11" spans="3:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="3:24" x14ac:dyDescent="0.3">
       <c r="L11" s="1">
         <f ca="1">L7+1</f>
-        <v>45646</v>
+        <v>45926</v>
       </c>
       <c r="N11" t="s">
         <v>10</v>
       </c>
       <c r="P11" s="7">
         <f ca="1">EOMONTH(P9,1)</f>
-        <v>45688</v>
-      </c>
-    </row>
-    <row r="12" spans="3:24" x14ac:dyDescent="0.35">
+        <v>45961</v>
+      </c>
+    </row>
+    <row r="12" spans="3:24" x14ac:dyDescent="0.3">
       <c r="L12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45041</v>
+        <v>44606</v>
       </c>
       <c r="P12" s="7">
         <f ca="1">EOMONTH(P10,-1)</f>
-        <v>45626</v>
-      </c>
-    </row>
-    <row r="13" spans="3:24" x14ac:dyDescent="0.35">
+        <v>45900</v>
+      </c>
+    </row>
+    <row r="13" spans="3:24" x14ac:dyDescent="0.3">
       <c r="L13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>44862</v>
+        <v>45459</v>
       </c>
       <c r="P13" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>45071</v>
-      </c>
-    </row>
-    <row r="14" spans="3:24" x14ac:dyDescent="0.35">
+        <v>45305</v>
+      </c>
+    </row>
+    <row r="14" spans="3:24" x14ac:dyDescent="0.3">
       <c r="L14" s="1">
         <f ca="1">EDATE(L7,-1)</f>
-        <v>45615</v>
+        <v>45894</v>
       </c>
       <c r="N14" t="s">
         <v>8</v>
       </c>
       <c r="P14" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>45884</v>
-      </c>
-    </row>
-    <row r="15" spans="3:24" x14ac:dyDescent="0.35">
+        <v>45919</v>
+      </c>
+    </row>
+    <row r="15" spans="3:24" x14ac:dyDescent="0.3">
       <c r="L15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45248</v>
+        <v>45945</v>
       </c>
       <c r="P15" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>45252</v>
-      </c>
-    </row>
-    <row r="16" spans="3:24" x14ac:dyDescent="0.35">
+        <v>45857</v>
+      </c>
+    </row>
+    <row r="16" spans="3:24" x14ac:dyDescent="0.3">
       <c r="L16" s="1">
         <f ca="1">EDATE(L7,1)</f>
-        <v>45676</v>
+        <v>45955</v>
       </c>
       <c r="N16" t="s">
         <v>11</v>
       </c>
       <c r="P16" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>45674</v>
-      </c>
-    </row>
-    <row r="17" spans="12:16" x14ac:dyDescent="0.35">
+        <v>45092</v>
+      </c>
+    </row>
+    <row r="17" spans="12:16" x14ac:dyDescent="0.3">
       <c r="L17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45539</v>
+        <v>45788</v>
       </c>
       <c r="P17" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>44961</v>
-      </c>
-    </row>
-    <row r="18" spans="12:16" x14ac:dyDescent="0.35">
+        <v>44746</v>
+      </c>
+    </row>
+    <row r="18" spans="12:16" x14ac:dyDescent="0.3">
       <c r="L18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45000</v>
+        <v>44901</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="L5:L18">
-    <cfRule type="timePeriod" dxfId="272" priority="6" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="22" priority="6" timePeriod="lastMonth">
       <formula>AND(MONTH(L5)=MONTH(EDATE(TODAY(),0-1)),YEAR(L5)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="271" priority="7" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="21" priority="7" timePeriod="nextMonth">
       <formula>AND(MONTH(L5)=MONTH(EDATE(TODAY(),0+1)),YEAR(L5)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="270" priority="8" timePeriod="tomorrow">
+    <cfRule type="timePeriod" dxfId="20" priority="8" timePeriod="tomorrow">
       <formula>FLOOR(L5,1)=TODAY()+1</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="269" priority="9" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="19" priority="9" timePeriod="today">
       <formula>FLOOR(L5,1)=TODAY()</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="268" priority="10" timePeriod="yesterday">
+    <cfRule type="timePeriod" dxfId="18" priority="10" timePeriod="yesterday">
       <formula>FLOOR(L5,1)=TODAY()-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:P17">
-    <cfRule type="timePeriod" dxfId="267" priority="1" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="17" priority="1" timePeriod="lastMonth">
       <formula>AND(MONTH(P5)=MONTH(EDATE(TODAY(),0-1)),YEAR(P5)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="266" priority="2" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="16" priority="2" timePeriod="nextMonth">
       <formula>AND(MONTH(P5)=MONTH(EDATE(TODAY(),0+1)),YEAR(P5)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="265" priority="3" timePeriod="tomorrow">
+    <cfRule type="timePeriod" dxfId="15" priority="3" timePeriod="tomorrow">
       <formula>FLOOR(P5,1)=TODAY()+1</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="264" priority="4" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="14" priority="4" timePeriod="today">
       <formula>FLOOR(P5,1)=TODAY()</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="263" priority="5" timePeriod="yesterday">
+    <cfRule type="timePeriod" dxfId="13" priority="5" timePeriod="yesterday">
       <formula>FLOOR(P5,1)=TODAY()-1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5863,13 +4094,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{495E616F-061B-4F8C-9F2A-0F625C26A7EF}">
   <dimension ref="A2:U35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
         <v>33</v>
       </c>
@@ -5911,7 +4142,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>35</v>
       </c>
@@ -5953,7 +4184,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>36</v>
       </c>
@@ -5995,7 +4226,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>37</v>
       </c>
@@ -6037,7 +4268,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>38</v>
       </c>
@@ -6079,7 +4310,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>39</v>
       </c>
@@ -6121,7 +4352,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>40</v>
       </c>
@@ -6163,7 +4394,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>41</v>
       </c>
@@ -6205,7 +4436,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>42</v>
       </c>
@@ -6247,7 +4478,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>43</v>
       </c>
@@ -6289,7 +4520,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>44</v>
       </c>
@@ -6331,7 +4562,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>45</v>
       </c>
@@ -6373,7 +4604,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>46</v>
       </c>
@@ -6415,7 +4646,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>47</v>
       </c>
@@ -6457,7 +4688,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>48</v>
       </c>
@@ -6500,7 +4731,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>49</v>
       </c>
@@ -6536,7 +4767,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="23" t="s">
         <v>33</v>
       </c>
@@ -6550,7 +4781,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="23" t="s">
         <v>35</v>
       </c>
@@ -6564,7 +4795,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="23" t="s">
         <v>36</v>
       </c>
@@ -6578,7 +4809,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="23" t="s">
         <v>37</v>
       </c>
@@ -6592,7 +4823,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="23" t="s">
         <v>38</v>
       </c>
@@ -6606,7 +4837,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="23" t="s">
         <v>39</v>
       </c>
@@ -6620,7 +4851,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="23" t="s">
         <v>40</v>
       </c>
@@ -6634,7 +4865,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="23" t="s">
         <v>41</v>
       </c>
@@ -6648,7 +4879,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="23" t="s">
         <v>42</v>
       </c>
@@ -6662,7 +4893,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="23" t="s">
         <v>43</v>
       </c>
@@ -6676,7 +4907,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="23" t="s">
         <v>44</v>
       </c>
@@ -6690,7 +4921,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
         <v>45</v>
       </c>
@@ -6704,7 +4935,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="23" t="s">
         <v>46</v>
       </c>
@@ -6718,7 +4949,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="23" t="s">
         <v>47</v>
       </c>
@@ -6732,7 +4963,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
         <v>48</v>
       </c>
@@ -6746,7 +4977,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="23" t="s">
         <v>49</v>
       </c>
@@ -6763,66 +4994,66 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A3:A17">
-    <cfRule type="expression" dxfId="24" priority="13">
+    <cfRule type="expression" dxfId="12" priority="13">
       <formula>$B3&lt;35</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A21:A35">
+    <cfRule type="expression" dxfId="11" priority="1">
+      <formula>$B21&gt;34</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B3:B17">
-    <cfRule type="cellIs" dxfId="23" priority="14" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="14" operator="lessThan">
       <formula>35</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B21:B35">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
+      <formula>34</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E3:E17">
-    <cfRule type="expression" dxfId="22" priority="11">
+    <cfRule type="expression" dxfId="8" priority="11">
       <formula>$F3&lt;34</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E21:E35">
+    <cfRule type="expression" dxfId="7" priority="3">
+      <formula>$F21&lt;35</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F3:F17">
-    <cfRule type="cellIs" dxfId="21" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="12" operator="lessThan">
       <formula>35</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F21:F35">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
+      <formula>35</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L3:N17">
-    <cfRule type="expression" dxfId="20" priority="8">
+    <cfRule type="expression" dxfId="4" priority="8">
       <formula>$M3&gt;74</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="9">
+    <cfRule type="expression" dxfId="3" priority="9">
       <formula>$L$6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3:P17">
-    <cfRule type="expression" dxfId="18" priority="6">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>$Q3&lt;35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q3:Q17">
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="lessThan">
       <formula>35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3:U16">
-    <cfRule type="expression" dxfId="16" priority="5">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>$U3&lt;$S3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F35">
-    <cfRule type="cellIs" dxfId="15" priority="4" operator="lessThan">
-      <formula>35</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E21:E35">
-    <cfRule type="expression" dxfId="14" priority="3">
-      <formula>$F21&lt;35</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B21:B35">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="greaterThan">
-      <formula>34</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A21:A35">
-    <cfRule type="expression" dxfId="12" priority="1">
-      <formula>$B21&gt;34</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6832,14 +5063,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D8FD89-9564-4047-8961-F5E555AD0B97}">
   <dimension ref="C1:O34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:15" x14ac:dyDescent="0.3">
       <c r="G1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>13</v>
       </c>
@@ -6862,7 +5093,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
@@ -6873,7 +5104,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C5">
         <v>34</v>
       </c>
@@ -6896,7 +5127,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C6">
         <v>98</v>
       </c>
@@ -6919,7 +5150,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C7">
         <v>25</v>
       </c>
@@ -6942,7 +5173,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C8">
         <v>89</v>
       </c>
@@ -6965,7 +5196,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C9">
         <v>45</v>
       </c>
@@ -6988,7 +5219,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C10">
         <v>81</v>
       </c>
@@ -7011,7 +5242,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C11">
         <v>6</v>
       </c>
@@ -7034,7 +5265,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C12">
         <v>17</v>
       </c>
@@ -7057,7 +5288,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C13">
         <v>33</v>
       </c>
@@ -7080,7 +5311,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C14">
         <v>53</v>
       </c>
@@ -7103,7 +5334,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C15">
         <v>9</v>
       </c>
@@ -7126,7 +5357,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C16">
         <v>16</v>
       </c>
@@ -7149,7 +5380,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C17">
         <v>36</v>
       </c>
@@ -7172,7 +5403,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C18">
         <v>57</v>
       </c>
@@ -7195,7 +5426,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C21">
         <v>34</v>
       </c>
@@ -7218,7 +5449,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C22">
         <v>98</v>
       </c>
@@ -7241,7 +5472,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C23">
         <v>25</v>
       </c>
@@ -7264,7 +5495,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C24">
         <v>89</v>
       </c>
@@ -7287,7 +5518,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C25">
         <v>45</v>
       </c>
@@ -7310,7 +5541,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C26">
         <v>81</v>
       </c>
@@ -7333,7 +5564,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C27">
         <v>6</v>
       </c>
@@ -7356,7 +5587,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C28">
         <v>17</v>
       </c>
@@ -7379,7 +5610,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C29">
         <v>33</v>
       </c>
@@ -7402,7 +5633,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C30">
         <v>53</v>
       </c>
@@ -7425,7 +5656,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C31">
         <v>9</v>
       </c>
@@ -7448,7 +5679,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C32">
         <v>16</v>
       </c>
@@ -7471,7 +5702,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C33">
         <v>36</v>
       </c>
@@ -7494,7 +5725,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C34">
         <v>57</v>
       </c>
@@ -7519,74 +5750,74 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C5:C18">
-    <cfRule type="cellIs" dxfId="296" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="100" priority="8" operator="greaterThan">
       <formula>34</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="295" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="99" priority="9" operator="lessThan">
       <formula>35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:C34">
-    <cfRule type="cellIs" dxfId="294" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="98" priority="7" operator="lessThan">
       <formula>35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E18">
-    <cfRule type="cellIs" dxfId="293" priority="15" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="97" priority="15" operator="greaterThan">
       <formula>34</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="292" priority="16" operator="lessThan">
+    <cfRule type="cellIs" dxfId="96" priority="16" operator="lessThan">
       <formula>35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21:E34">
-    <cfRule type="cellIs" dxfId="291" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="95" priority="6" operator="greaterThan">
       <formula>34</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G18">
-    <cfRule type="cellIs" dxfId="290" priority="14" operator="between">
+    <cfRule type="cellIs" dxfId="94" priority="14" operator="between">
       <formula>60</formula>
       <formula>74</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G21:G34">
-    <cfRule type="cellIs" dxfId="289" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="93" priority="5" operator="between">
       <formula>60</formula>
       <formula>74</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I18">
-    <cfRule type="cellIs" dxfId="288" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="12" operator="equal">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I21:I34">
-    <cfRule type="cellIs" dxfId="287" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="4" operator="equal">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K18">
-    <cfRule type="containsText" dxfId="286" priority="13" operator="containsText" text="A">
+    <cfRule type="containsText" dxfId="90" priority="13" operator="containsText" text="A">
       <formula>NOT(ISERROR(SEARCH("A",K5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21:K34">
-    <cfRule type="containsText" dxfId="285" priority="3" operator="containsText" text="A">
+    <cfRule type="containsText" dxfId="89" priority="3" operator="containsText" text="A">
       <formula>NOT(ISERROR(SEARCH("A",K21)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5:M18">
-    <cfRule type="duplicateValues" dxfId="284" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M21:M34">
-    <cfRule type="duplicateValues" dxfId="283" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O5:O18">
-    <cfRule type="uniqueValues" dxfId="282" priority="10"/>
+    <cfRule type="uniqueValues" dxfId="86" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O21:O34">
-    <cfRule type="uniqueValues" dxfId="281" priority="1"/>
+    <cfRule type="uniqueValues" dxfId="85" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7595,19 +5826,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{458FE0A0-83F2-41E2-8F96-CB4593002587}">
   <dimension ref="B1:K17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="K1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>53</v>
       </c>
@@ -7618,7 +5849,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>34</v>
       </c>
@@ -7642,12 +5873,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>98</v>
       </c>
       <c r="C5">
-        <f t="shared" ref="C4:C17" si="0">COUNTIFS(B:B,B5)</f>
+        <f t="shared" ref="C5:C17" si="0">COUNTIFS(B:B,B5)</f>
         <v>1</v>
       </c>
       <c r="D5" t="str">
@@ -7666,7 +5897,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>34</v>
       </c>
@@ -7690,7 +5921,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>55</v>
       </c>
@@ -7714,7 +5945,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>25</v>
       </c>
@@ -7738,7 +5969,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>81</v>
       </c>
@@ -7762,7 +5993,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>6</v>
       </c>
@@ -7786,7 +6017,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>75</v>
       </c>
@@ -7810,7 +6041,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>33</v>
       </c>
@@ -7834,7 +6065,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>73</v>
       </c>
@@ -7858,7 +6089,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>34</v>
       </c>
@@ -7882,7 +6113,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>16</v>
       </c>
@@ -7903,7 +6134,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>75</v>
       </c>
@@ -7924,7 +6155,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>57</v>
       </c>
@@ -7947,10 +6178,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:B17">
-    <cfRule type="duplicateValues" dxfId="280" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K14">
-    <cfRule type="duplicateValues" dxfId="279" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7959,20 +6190,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE0A86EB-DF61-423C-9250-83E95D2AA6D1}">
   <dimension ref="A1:T21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="10.08984375" customWidth="1"/>
-    <col min="7" max="7" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="10.109375" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
         <v>2</v>
       </c>
@@ -7980,19 +6211,19 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="E3" s="7">
         <f ca="1">DATE(RANDBETWEEN(2023,2025),RANDBETWEEN(1,12),RANDBETWEEN(1,28))</f>
-        <v>45226</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+        <v>45527</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45851</v>
       </c>
       <c r="C5" s="7">
         <f ca="1">TODAY()</f>
-        <v>45645</v>
+        <v>45925</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="1">
@@ -8010,10 +6241,10 @@
       </c>
       <c r="N5" s="1">
         <f ca="1">TODAY()</f>
-        <v>45645</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>44786</v>
       </c>
@@ -8037,7 +6268,7 @@
         <v>45635</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45080</v>
       </c>
@@ -8046,7 +6277,7 @@
       </c>
       <c r="G7" s="1">
         <f t="shared" ref="G7:G19" ca="1" si="0">DATE(RANDBETWEEN(2022,2025),RANDBETWEEN(1,12),RANDBETWEEN(1,28))</f>
-        <v>45718</v>
+        <v>44875</v>
       </c>
       <c r="I7" s="1">
         <v>45958</v>
@@ -8055,7 +6286,7 @@
         <v>45238</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>44811</v>
       </c>
@@ -8065,7 +6296,7 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45609</v>
+        <v>45911</v>
       </c>
       <c r="I8" s="1">
         <v>45781</v>
@@ -8077,18 +6308,18 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f ca="1">TODAY()</f>
-        <v>45645</v>
+        <v>45925</v>
       </c>
       <c r="E9" s="1">
         <f ca="1">TODAY()</f>
-        <v>45645</v>
+        <v>45925</v>
       </c>
       <c r="G9" s="1">
         <f ca="1">TODAY()</f>
-        <v>45645</v>
+        <v>45925</v>
       </c>
       <c r="I9" s="1">
         <v>45568</v>
@@ -8106,17 +6337,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f ca="1">A9-1</f>
-        <v>45644</v>
+        <v>45924</v>
       </c>
       <c r="E10" s="1">
         <v>45674</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45066</v>
+        <v>45373</v>
       </c>
       <c r="I10" s="1">
         <v>45710</v>
@@ -8140,18 +6371,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f ca="1">A9+1</f>
-        <v>45646</v>
+        <v>45926</v>
       </c>
       <c r="E11" s="1">
         <f ca="1">E9+1</f>
-        <v>45646</v>
+        <v>45926</v>
       </c>
       <c r="G11" s="1">
         <f ca="1">G9+1</f>
-        <v>45646</v>
+        <v>45926</v>
       </c>
       <c r="I11" s="1">
         <v>45569</v>
@@ -8160,7 +6391,7 @@
         <v>45639</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>45871</v>
       </c>
@@ -8169,7 +6400,7 @@
       </c>
       <c r="G12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45931</v>
+        <v>45860</v>
       </c>
       <c r="I12" s="1">
         <v>45739</v>
@@ -8185,17 +6416,17 @@
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>45613</v>
       </c>
       <c r="E13" s="1">
         <f ca="1">E9-1</f>
-        <v>45644</v>
+        <v>45924</v>
       </c>
       <c r="G13" s="1">
         <f ca="1">G9-1</f>
-        <v>45644</v>
+        <v>45924</v>
       </c>
       <c r="I13" s="1">
         <v>45567</v>
@@ -8207,7 +6438,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>44688</v>
       </c>
@@ -8216,7 +6447,7 @@
       </c>
       <c r="G14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>44701</v>
+        <v>45306</v>
       </c>
       <c r="I14" s="1">
         <v>45491</v>
@@ -8225,17 +6456,17 @@
         <v>45318</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>45643</v>
       </c>
       <c r="E15" s="1">
         <f ca="1">EDATE(E9,1)</f>
-        <v>45676</v>
+        <v>45955</v>
       </c>
       <c r="G15" s="1">
         <f ca="1">EOMONTH(G9,1)</f>
-        <v>45688</v>
+        <v>45961</v>
       </c>
       <c r="I15" s="1">
         <v>45626</v>
@@ -8245,10 +6476,10 @@
       </c>
       <c r="L15" s="7">
         <f ca="1">TODAY()</f>
-        <v>45645</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>45582</v>
       </c>
@@ -8257,7 +6488,7 @@
       </c>
       <c r="G16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45696</v>
+        <v>45704</v>
       </c>
       <c r="I16" s="1">
         <v>45013</v>
@@ -8266,17 +6497,17 @@
         <v>44610</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>45583</v>
       </c>
       <c r="E17" s="1">
         <f ca="1">EDATE(E9,-1)</f>
-        <v>45615</v>
+        <v>45894</v>
       </c>
       <c r="G17" s="1">
         <f ca="1">EDATE(G9,-1)</f>
-        <v>45615</v>
+        <v>45894</v>
       </c>
       <c r="I17" s="1">
         <v>45538</v>
@@ -8294,7 +6525,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>45427</v>
       </c>
@@ -8303,7 +6534,7 @@
       </c>
       <c r="G18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>45035</v>
+        <v>44797</v>
       </c>
       <c r="I18" s="1">
         <v>45551</v>
@@ -8326,7 +6557,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>45651</v>
       </c>
@@ -8335,7 +6566,7 @@
       </c>
       <c r="G19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>44586</v>
+        <v>45841</v>
       </c>
       <c r="I19" s="1">
         <v>45737</v>
@@ -8344,101 +6575,101 @@
         <v>44965</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="N20" s="24">
         <f>DATE(N18,P18,R18)</f>
         <v>45645</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="N21" t="s">
         <v>76</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A5:A19">
-    <cfRule type="timePeriod" dxfId="262" priority="11" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="82" priority="11" timePeriod="nextMonth">
       <formula>AND(MONTH(A5)=MONTH(EDATE(TODAY(),0+1)),YEAR(A5)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="261" priority="12" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="81" priority="12" timePeriod="lastMonth">
       <formula>AND(MONTH(A5)=MONTH(EDATE(TODAY(),0-1)),YEAR(A5)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="260" priority="13" timePeriod="tomorrow">
+    <cfRule type="timePeriod" dxfId="80" priority="13" timePeriod="tomorrow">
       <formula>FLOOR(A5,1)=TODAY()+1</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="259" priority="14" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="79" priority="14" timePeriod="today">
       <formula>FLOOR(A5,1)=TODAY()</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="258" priority="15" timePeriod="yesterday">
+    <cfRule type="timePeriod" dxfId="78" priority="15" timePeriod="yesterday">
       <formula>FLOOR(A5,1)=TODAY()-1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E19">
+    <cfRule type="timePeriod" dxfId="77" priority="1" timePeriod="nextMonth">
+      <formula>AND(MONTH(E5)=MONTH(EDATE(TODAY(),0+1)),YEAR(E5)=YEAR(EDATE(TODAY(),0+1)))</formula>
+    </cfRule>
+    <cfRule type="timePeriod" dxfId="76" priority="2" timePeriod="lastMonth">
+      <formula>AND(MONTH(E5)=MONTH(EDATE(TODAY(),0-1)),YEAR(E5)=YEAR(EDATE(TODAY(),0-1)))</formula>
+    </cfRule>
+    <cfRule type="timePeriod" dxfId="75" priority="3" timePeriod="tomorrow">
+      <formula>FLOOR(E5,1)=TODAY()+1</formula>
+    </cfRule>
+    <cfRule type="timePeriod" dxfId="74" priority="4" timePeriod="today">
+      <formula>FLOOR(E5,1)=TODAY()</formula>
+    </cfRule>
+    <cfRule type="timePeriod" dxfId="73" priority="5" timePeriod="yesterday">
+      <formula>FLOOR(E5,1)=TODAY()-1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G5:G19">
-    <cfRule type="timePeriod" dxfId="257" priority="21" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="72" priority="21" timePeriod="nextMonth">
       <formula>AND(MONTH(G5)=MONTH(EDATE(TODAY(),0+1)),YEAR(G5)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="256" priority="22" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="71" priority="22" timePeriod="lastMonth">
       <formula>AND(MONTH(G5)=MONTH(EDATE(TODAY(),0-1)),YEAR(G5)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="255" priority="23" timePeriod="tomorrow">
+    <cfRule type="timePeriod" dxfId="70" priority="23" timePeriod="tomorrow">
       <formula>FLOOR(G5,1)=TODAY()+1</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="254" priority="24" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="69" priority="24" timePeriod="today">
       <formula>FLOOR(G5,1)=TODAY()</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="253" priority="25" timePeriod="yesterday">
+    <cfRule type="timePeriod" dxfId="68" priority="25" timePeriod="yesterday">
       <formula>FLOOR(G5,1)=TODAY()-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I19">
-    <cfRule type="timePeriod" dxfId="252" priority="16" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="67" priority="16" timePeriod="nextMonth">
       <formula>AND(MONTH(I5)=MONTH(EDATE(TODAY(),0+1)),YEAR(I5)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="251" priority="17" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="66" priority="17" timePeriod="lastMonth">
       <formula>AND(MONTH(I5)=MONTH(EDATE(TODAY(),0-1)),YEAR(I5)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="250" priority="18" timePeriod="tomorrow">
+    <cfRule type="timePeriod" dxfId="65" priority="18" timePeriod="tomorrow">
       <formula>FLOOR(I5,1)=TODAY()+1</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="249" priority="19" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="64" priority="19" timePeriod="today">
       <formula>FLOOR(I5,1)=TODAY()</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="248" priority="20" timePeriod="yesterday">
+    <cfRule type="timePeriod" dxfId="63" priority="20" timePeriod="yesterday">
       <formula>FLOOR(I5,1)=TODAY()-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K19">
-    <cfRule type="timePeriod" dxfId="247" priority="6" timePeriod="nextMonth">
+    <cfRule type="timePeriod" dxfId="62" priority="6" timePeriod="nextMonth">
       <formula>AND(MONTH(K5)=MONTH(EDATE(TODAY(),0+1)),YEAR(K5)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="246" priority="7" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="61" priority="7" timePeriod="lastMonth">
       <formula>AND(MONTH(K5)=MONTH(EDATE(TODAY(),0-1)),YEAR(K5)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="245" priority="8" timePeriod="tomorrow">
+    <cfRule type="timePeriod" dxfId="60" priority="8" timePeriod="tomorrow">
       <formula>FLOOR(K5,1)=TODAY()+1</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="244" priority="9" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="59" priority="9" timePeriod="today">
       <formula>FLOOR(K5,1)=TODAY()</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="243" priority="10" timePeriod="yesterday">
+    <cfRule type="timePeriod" dxfId="58" priority="10" timePeriod="yesterday">
       <formula>FLOOR(K5,1)=TODAY()-1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E19">
-    <cfRule type="timePeriod" dxfId="238" priority="5" timePeriod="yesterday">
-      <formula>FLOOR(E5,1)=TODAY()-1</formula>
-    </cfRule>
-    <cfRule type="timePeriod" dxfId="239" priority="4" timePeriod="today">
-      <formula>FLOOR(E5,1)=TODAY()</formula>
-    </cfRule>
-    <cfRule type="timePeriod" dxfId="240" priority="3" timePeriod="tomorrow">
-      <formula>FLOOR(E5,1)=TODAY()+1</formula>
-    </cfRule>
-    <cfRule type="timePeriod" dxfId="241" priority="2" timePeriod="lastMonth">
-      <formula>AND(MONTH(E5)=MONTH(EDATE(TODAY(),0-1)),YEAR(E5)=YEAR(EDATE(TODAY(),0-1)))</formula>
-    </cfRule>
-    <cfRule type="timePeriod" dxfId="242" priority="1" timePeriod="nextMonth">
-      <formula>AND(MONTH(E5)=MONTH(EDATE(TODAY(),0+1)),YEAR(E5)=YEAR(EDATE(TODAY(),0+1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8451,16 +6682,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC8A9EFC-CF15-4DDA-9A36-BDF1D136C881}">
   <dimension ref="B1:Y34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.7265625" style="8"/>
-    <col min="4" max="4" width="8.7265625" style="9"/>
-    <col min="7" max="7" width="8.7265625" style="13"/>
-    <col min="9" max="9" width="8.7265625" style="14"/>
-    <col min="21" max="21" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" style="8"/>
+    <col min="4" max="4" width="8.77734375" style="9"/>
+    <col min="7" max="7" width="8.77734375" style="13"/>
+    <col min="9" max="9" width="8.77734375" style="14"/>
+    <col min="21" max="21" width="17.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="10" t="s">
         <v>26</v>
       </c>
@@ -8475,7 +6706,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B2" s="13"/>
       <c r="D2" s="14"/>
       <c r="G2" s="10" t="s">
@@ -8494,7 +6725,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B3" s="13">
         <v>63</v>
       </c>
@@ -8520,7 +6751,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B4" s="13">
         <v>25</v>
       </c>
@@ -8546,7 +6777,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B5" s="13">
         <v>23</v>
       </c>
@@ -8572,7 +6803,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B6" s="13">
         <v>100</v>
       </c>
@@ -8598,7 +6829,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B7" s="13">
         <v>48</v>
       </c>
@@ -8624,7 +6855,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B8" s="13">
         <v>71</v>
       </c>
@@ -8650,7 +6881,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B9" s="13">
         <v>36</v>
       </c>
@@ -8676,7 +6907,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B10" s="13">
         <v>95</v>
       </c>
@@ -8702,7 +6933,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B11" s="13">
         <v>56</v>
       </c>
@@ -8728,7 +6959,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B12" s="13">
         <v>79</v>
       </c>
@@ -8754,7 +6985,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B13" s="13">
         <v>96</v>
       </c>
@@ -8780,7 +7011,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B14" s="13">
         <v>45</v>
       </c>
@@ -8806,7 +7037,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B15" s="13">
         <v>65</v>
       </c>
@@ -8832,7 +7063,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B16" s="13">
         <v>74</v>
       </c>
@@ -8858,7 +7089,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="15">
         <v>34</v>
       </c>
@@ -8886,7 +7117,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:25" x14ac:dyDescent="0.3">
       <c r="G19" s="13" t="s">
         <v>79</v>
       </c>
@@ -8909,7 +7140,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B20" s="8">
         <v>63</v>
       </c>
@@ -8947,7 +7178,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B21" s="8">
         <v>25</v>
       </c>
@@ -8985,7 +7216,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B22" s="8">
         <v>23</v>
       </c>
@@ -9023,7 +7254,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B23" s="8">
         <v>100</v>
       </c>
@@ -9061,7 +7292,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B24" s="8">
         <v>48</v>
       </c>
@@ -9099,7 +7330,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B25" s="8">
         <v>71</v>
       </c>
@@ -9137,7 +7368,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B26" s="8">
         <v>36</v>
       </c>
@@ -9175,7 +7406,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B27" s="8">
         <v>95</v>
       </c>
@@ -9213,7 +7444,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B28" s="8">
         <v>56</v>
       </c>
@@ -9251,7 +7482,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B29" s="8">
         <v>79</v>
       </c>
@@ -9289,7 +7520,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B30" s="8">
         <v>96</v>
       </c>
@@ -9327,7 +7558,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B31" s="8">
         <v>45</v>
       </c>
@@ -9365,7 +7596,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B32" s="8">
         <v>65</v>
       </c>
@@ -9403,7 +7634,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B33" s="8">
         <v>74</v>
       </c>
@@ -9441,7 +7672,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B34" s="8">
         <v>34</v>
       </c>
@@ -9484,66 +7715,66 @@
     <sortCondition descending="1" ref="W20:W34"/>
   </sortState>
   <conditionalFormatting sqref="B3:B17">
-    <cfRule type="top10" dxfId="135" priority="47" rank="5"/>
+    <cfRule type="top10" dxfId="57" priority="47" rank="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20:B34">
+    <cfRule type="top10" dxfId="56" priority="12" rank="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D17">
-    <cfRule type="top10" dxfId="134" priority="46" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="55" priority="46" bottom="1" rank="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20:D34">
+    <cfRule type="top10" dxfId="54" priority="11" bottom="1" rank="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G17">
-    <cfRule type="top10" dxfId="133" priority="45" rank="5"/>
+    <cfRule type="top10" dxfId="53" priority="45" rank="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20:G34">
+    <cfRule type="top10" dxfId="52" priority="10" rank="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I17">
-    <cfRule type="top10" dxfId="132" priority="44" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="51" priority="44" bottom="1" rank="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I20:I34">
+    <cfRule type="top10" dxfId="50" priority="9" bottom="1" rank="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K17">
-    <cfRule type="top10" dxfId="131" priority="40" percent="1" bottom="1" rank="50"/>
-    <cfRule type="top10" dxfId="130" priority="43" percent="1" rank="50"/>
+    <cfRule type="top10" dxfId="49" priority="40" percent="1" bottom="1" rank="50"/>
+    <cfRule type="top10" dxfId="48" priority="43" percent="1" rank="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K20:K34">
+    <cfRule type="top10" dxfId="47" priority="8" percent="1" rank="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M20:M34">
+    <cfRule type="top10" dxfId="46" priority="7" percent="1" rank="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O20:O34">
+    <cfRule type="top10" dxfId="45" priority="6" percent="1" bottom="1" rank="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q20:Q34">
+    <cfRule type="aboveAverage" dxfId="44" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S20:S34">
+    <cfRule type="aboveAverage" dxfId="43" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3:U17">
-    <cfRule type="aboveAverage" dxfId="129" priority="38" aboveAverage="0"/>
-    <cfRule type="aboveAverage" dxfId="128" priority="39"/>
+    <cfRule type="aboveAverage" dxfId="42" priority="38" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="41" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U20:U34">
+    <cfRule type="aboveAverage" dxfId="40" priority="3" aboveAverage="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W3:W17">
-    <cfRule type="top10" dxfId="127" priority="42" percent="1" rank="50"/>
+    <cfRule type="top10" dxfId="39" priority="42" percent="1" rank="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W20:W34">
+    <cfRule type="aboveAverage" dxfId="38" priority="2" aboveAverage="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y3:Y17">
-    <cfRule type="top10" dxfId="126" priority="41" percent="1" bottom="1" rank="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B20:B34">
-    <cfRule type="top10" dxfId="125" priority="12" rank="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D20:D34">
-    <cfRule type="top10" dxfId="124" priority="11" bottom="1" rank="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G20:G34">
-    <cfRule type="top10" dxfId="123" priority="10" rank="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I20:I34">
-    <cfRule type="top10" dxfId="122" priority="9" bottom="1" rank="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K20:K34">
-    <cfRule type="top10" dxfId="121" priority="8" percent="1" rank="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M20:M34">
-    <cfRule type="top10" dxfId="120" priority="7" percent="1" rank="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O20:O34">
-    <cfRule type="top10" dxfId="119" priority="6" percent="1" bottom="1" rank="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q20:Q34">
-    <cfRule type="aboveAverage" dxfId="118" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S20:S34">
-    <cfRule type="aboveAverage" dxfId="117" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U20:U34">
-    <cfRule type="aboveAverage" dxfId="116" priority="3" aboveAverage="0"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W20:W34">
-    <cfRule type="aboveAverage" dxfId="115" priority="2" aboveAverage="0"/>
+    <cfRule type="top10" dxfId="37" priority="41" percent="1" bottom="1" rank="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y20:Y34">
-    <cfRule type="aboveAverage" dxfId="93" priority="1"/>
+    <cfRule type="aboveAverage" dxfId="36" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9552,12 +7783,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738D80BB-FA0E-4420-A1EE-4B347D9836BE}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E1" t="s">
         <v>84</v>
       </c>
@@ -9568,7 +7799,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G2" t="s">
         <v>81</v>
       </c>
@@ -9576,7 +7807,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>77</v>
       </c>
@@ -9590,7 +7821,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="25">
         <v>1</v>
       </c>
@@ -9609,7 +7840,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="25">
         <v>2</v>
       </c>
@@ -9628,7 +7859,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="25">
         <v>3</v>
       </c>
@@ -9647,7 +7878,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="25">
         <v>4</v>
       </c>
@@ -9666,7 +7897,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="25">
         <v>5</v>
       </c>
@@ -9685,7 +7916,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="25">
         <v>6</v>
       </c>
@@ -9704,7 +7935,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="25">
         <v>7</v>
       </c>
@@ -9723,7 +7954,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="25">
         <v>8</v>
       </c>
@@ -9742,7 +7973,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="25">
         <v>9</v>
       </c>
@@ -9761,7 +7992,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="25">
         <v>10</v>
       </c>
@@ -9780,7 +8011,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="25">
         <v>11</v>
       </c>
@@ -9799,7 +8030,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="25">
         <v>12</v>
       </c>
@@ -9818,7 +8049,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="25">
         <v>13</v>
       </c>
@@ -9837,7 +8068,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="25">
         <v>14</v>
       </c>
@@ -9856,7 +8087,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="25">
         <v>15</v>
       </c>
@@ -9886,9 +8117,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14FAB54A-744E-4BC5-8CD1-F8395B4A11C8}">
   <dimension ref="C1:Q32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
         <v>91</v>
       </c>
@@ -9899,7 +8130,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C3">
         <v>6</v>
       </c>
@@ -9925,7 +8156,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C4">
         <v>94</v>
       </c>
@@ -9951,7 +8182,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C5">
         <v>76</v>
       </c>
@@ -9977,7 +8208,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C6">
         <v>92</v>
       </c>
@@ -10003,7 +8234,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C7">
         <v>27</v>
       </c>
@@ -10029,7 +8260,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C8">
         <v>53</v>
       </c>
@@ -10055,7 +8286,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C9">
         <v>41</v>
       </c>
@@ -10081,7 +8312,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C10">
         <v>88</v>
       </c>
@@ -10107,7 +8338,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C11">
         <v>52</v>
       </c>
@@ -10133,7 +8364,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C12">
         <v>33</v>
       </c>
@@ -10159,7 +8390,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C13">
         <v>80</v>
       </c>
@@ -10185,7 +8416,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C14">
         <v>54</v>
       </c>
@@ -10211,7 +8442,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C15">
         <v>20</v>
       </c>
@@ -10237,7 +8468,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C16">
         <v>43</v>
       </c>
@@ -10263,7 +8494,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="9:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I19">
         <v>34</v>
       </c>
@@ -10280,7 +8511,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="9:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I20">
         <v>98</v>
       </c>
@@ -10297,7 +8528,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="21" spans="9:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I21">
         <v>25</v>
       </c>
@@ -10314,7 +8545,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="9:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I22">
         <v>89</v>
       </c>
@@ -10331,7 +8562,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="9:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I23">
         <v>45</v>
       </c>
@@ -10348,7 +8579,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="9:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I24">
         <v>81</v>
       </c>
@@ -10365,7 +8596,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="9:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I25">
         <v>6</v>
       </c>
@@ -10382,7 +8613,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="9:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I26">
         <v>17</v>
       </c>
@@ -10399,7 +8630,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="9:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I27">
         <v>33</v>
       </c>
@@ -10416,7 +8647,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="9:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I28">
         <v>53</v>
       </c>
@@ -10433,7 +8664,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="9:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I29">
         <v>9</v>
       </c>
@@ -10450,7 +8681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="9:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I30">
         <v>16</v>
       </c>
@@ -10467,7 +8698,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="9:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I31">
         <v>36</v>
       </c>
@@ -10484,7 +8715,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="9:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I32">
         <v>57</v>
       </c>
@@ -10506,13 +8737,27 @@
     <sortCondition ref="I3:I16"/>
   </sortState>
   <conditionalFormatting sqref="C3:C16">
-    <cfRule type="top10" dxfId="74" priority="20" percent="1" rank="50"/>
+    <cfRule type="top10" dxfId="35" priority="20" percent="1" rank="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E16">
-    <cfRule type="top10" dxfId="73" priority="19" percent="1" rank="50"/>
+    <cfRule type="top10" dxfId="34" priority="19" percent="1" rank="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G16">
-    <cfRule type="top10" dxfId="72" priority="18" percent="1" bottom="1" rank="50"/>
+    <cfRule type="top10" dxfId="33" priority="18" percent="1" bottom="1" rank="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I16">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{7BD94185-B7B2-4E08-BE44-26B57F225400}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I19:I32">
     <cfRule type="dataBar" priority="7">
@@ -10556,6 +8801,20 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="M3:M16">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{0D7F878E-6BA9-45A3-B9A0-71CD5E96BDC1}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M19:M32">
     <cfRule type="dataBar" priority="5">
       <dataBar>
@@ -10598,38 +8857,23 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I16">
-    <cfRule type="dataBar" priority="4">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF555A"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7BD94185-B7B2-4E08-BE44-26B57F225400}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M3:M16">
-    <cfRule type="dataBar" priority="3">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF008AEF"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0D7F878E-6BA9-45A3-B9A0-71CD5E96BDC1}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{7BD94185-B7B2-4E08-BE44-26B57F225400}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFF555A"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I3:I16</xm:sqref>
+        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{661987DD-E025-4D78-852D-120AE8C6C3D5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
@@ -10668,6 +8912,17 @@
           <xm:sqref>K19:K32</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{0D7F878E-6BA9-45A3-B9A0-71CD5E96BDC1}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>M3:M16</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{88F5521D-2FBA-49BE-8FAF-E516711762C8}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
@@ -10700,30 +8955,6 @@
           </x14:cfRule>
           <xm:sqref>Q3:Q16</xm:sqref>
         </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7BD94185-B7B2-4E08-BE44-26B57F225400}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FFFF555A"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>I3:I16</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0D7F878E-6BA9-45A3-B9A0-71CD5E96BDC1}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>M3:M16</xm:sqref>
-        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
@@ -10733,12 +8964,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B30011A-C36E-4E9D-A8E2-6477421A9F76}">
   <dimension ref="B1:N31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>31</v>
       </c>
@@ -10752,7 +8983,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2">
         <v>34</v>
       </c>
@@ -10775,7 +9006,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>98</v>
       </c>
@@ -10798,7 +9029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>25</v>
       </c>
@@ -10821,7 +9052,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>89</v>
       </c>
@@ -10844,7 +9075,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>45</v>
       </c>
@@ -10867,7 +9098,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>81</v>
       </c>
@@ -10890,7 +9121,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>6</v>
       </c>
@@ -10913,7 +9144,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>17</v>
       </c>
@@ -10936,7 +9167,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>33</v>
       </c>
@@ -10959,7 +9190,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>53</v>
       </c>
@@ -10982,7 +9213,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>9</v>
       </c>
@@ -11005,7 +9236,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>16</v>
       </c>
@@ -11028,7 +9259,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>36</v>
       </c>
@@ -11051,7 +9282,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>57</v>
       </c>
@@ -11074,7 +9305,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>85</v>
       </c>
@@ -11082,7 +9313,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>98</v>
       </c>
@@ -11105,7 +9336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>89</v>
       </c>
@@ -11128,7 +9359,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>81</v>
       </c>
@@ -11151,7 +9382,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>57</v>
       </c>
@@ -11174,7 +9405,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>53</v>
       </c>
@@ -11197,7 +9428,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>45</v>
       </c>
@@ -11220,7 +9451,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>36</v>
       </c>
@@ -11243,7 +9474,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>34</v>
       </c>
@@ -11266,7 +9497,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>33</v>
       </c>
@@ -11289,7 +9520,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>25</v>
       </c>
@@ -11312,7 +9543,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>17</v>
       </c>
@@ -11335,7 +9566,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>16</v>
       </c>
@@ -11358,7 +9589,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>9</v>
       </c>
@@ -11381,7 +9612,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>6</v>
       </c>
@@ -11420,6 +9651,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B18:B31">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D2:D15">
     <cfRule type="colorScale" priority="27">
       <colorScale>
@@ -11432,6 +9675,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D18:D31">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F2:F15">
     <cfRule type="colorScale" priority="24">
       <colorScale>
@@ -11444,6 +9699,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F18:F31">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H2:H15">
     <cfRule type="colorScale" priority="23">
       <colorScale>
@@ -11456,72 +9723,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J15">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEF9C"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L15">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEF9C"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N15">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEF9C"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B18:B31">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D18:D31">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F18:F31">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H18:H31">
     <cfRule type="colorScale" priority="3">
       <colorScale>
@@ -11534,6 +9735,16 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J15">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J18:J31">
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -11544,6 +9755,26 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L15">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N15">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="N18:N31">
     <cfRule type="colorScale" priority="1">
       <colorScale>
@@ -11561,9 +9792,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03BA59A0-79FB-4815-A613-5B583E5F5372}">
   <dimension ref="B2:Y31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2">
         <v>34</v>
       </c>
@@ -11586,7 +9817,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>98</v>
       </c>
@@ -11609,7 +9840,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>25</v>
       </c>
@@ -11632,7 +9863,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>89</v>
       </c>
@@ -11655,7 +9886,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>45</v>
       </c>
@@ -11678,7 +9909,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>81</v>
       </c>
@@ -11701,7 +9932,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>6</v>
       </c>
@@ -11724,7 +9955,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>17</v>
       </c>
@@ -11747,7 +9978,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>33</v>
       </c>
@@ -11770,7 +10001,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>53</v>
       </c>
@@ -11793,7 +10024,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>9</v>
       </c>
@@ -11816,7 +10047,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>16</v>
       </c>
@@ -11839,7 +10070,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>36</v>
       </c>
@@ -11862,7 +10093,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>57</v>
       </c>
@@ -11885,7 +10116,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:25" x14ac:dyDescent="0.3">
       <c r="P17" s="26" t="s">
         <v>86</v>
       </c>
@@ -11900,7 +10131,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>6</v>
       </c>
@@ -11939,7 +10170,7 @@
         <v>-92</v>
       </c>
     </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>9</v>
       </c>
@@ -11978,7 +10209,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>16</v>
       </c>
@@ -12017,7 +10248,7 @@
         <v>-65</v>
       </c>
     </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>17</v>
       </c>
@@ -12056,7 +10287,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>25</v>
       </c>
@@ -12095,7 +10326,7 @@
         <v>-28</v>
       </c>
     </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>33</v>
       </c>
@@ -12134,7 +10365,7 @@
         <v>-12</v>
       </c>
     </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>34</v>
       </c>
@@ -12173,7 +10404,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>36</v>
       </c>
@@ -12212,7 +10443,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>45</v>
       </c>
@@ -12251,7 +10482,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>53</v>
       </c>
@@ -12290,7 +10521,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>57</v>
       </c>
@@ -12329,7 +10560,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>81</v>
       </c>
@@ -12368,7 +10599,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>89</v>
       </c>
@@ -12407,7 +10638,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>98</v>
       </c>
@@ -12450,8 +10681,26 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D2:D15">
     <sortCondition descending="1" ref="D2:D15"/>
   </sortState>
+  <conditionalFormatting sqref="B2:B15">
+    <cfRule type="iconSet" priority="5">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B18:B31">
     <cfRule type="iconSet" priority="16">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D15">
+    <cfRule type="iconSet" priority="4">
       <iconSet iconSet="3Arrows">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="33"/>
@@ -12581,24 +10830,6 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="Y18:Y31">
     <cfRule type="iconSet" priority="6">
-      <iconSet iconSet="3Arrows">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="33"/>
-        <cfvo type="percent" val="67"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B15">
-    <cfRule type="iconSet" priority="5">
-      <iconSet iconSet="3Arrows">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="33"/>
-        <cfvo type="percent" val="67"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D15">
-    <cfRule type="iconSet" priority="4">
       <iconSet iconSet="3Arrows">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="33"/>
